--- a/data/trans_dic/P1426-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1426-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,9</t>
+          <t>0,63; 3,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,02</t>
+          <t>1,07; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,5</t>
+          <t>0,91; 3,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,21</t>
+          <t>1,03; 4,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,47</t>
+          <t>1,31; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,6</t>
+          <t>1,08; 3,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,43</t>
+          <t>1,1; 3,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,4</t>
+          <t>1,5; 4,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,99</t>
+          <t>1,22; 2,99</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,51</t>
+          <t>0,15; 1,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,92</t>
+          <t>1,17; 3,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,65</t>
+          <t>1,5; 4,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,46</t>
+          <t>0,42; 2,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,13</t>
+          <t>1,01; 3,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,76</t>
+          <t>0,93; 2,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,57</t>
+          <t>0,37; 1,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,0</t>
+          <t>1,4; 3,12</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,12</t>
+          <t>0,43; 4,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,31</t>
+          <t>6,52; 12,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,35</t>
+          <t>0,59; 3,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,74</t>
+          <t>0,26; 2,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,93</t>
+          <t>4,01; 7,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,1</t>
+          <t>0,75; 2,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,73</t>
+          <t>0,28; 1,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,35</t>
+          <t>5,9; 9,11</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,2</t>
+          <t>0,26; 2,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,15</t>
+          <t>0,82; 4,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,32</t>
+          <t>1,58; 4,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,08</t>
+          <t>0,49; 2,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,76</t>
+          <t>2,84; 5,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,13</t>
+          <t>0,51; 2,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,7</t>
+          <t>0,62; 2,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,39</t>
+          <t>2,62; 4,7</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 7,1</t>
+          <t>1,53; 7,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 11,05</t>
+          <t>4,66; 10,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,7</t>
+          <t>2,85; 9,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,31</t>
+          <t>1,97; 7,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,51</t>
+          <t>5,64; 10,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,83</t>
+          <t>2,8; 7,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,59</t>
+          <t>1,39; 4,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,73</t>
+          <t>5,87; 9,29</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,66</t>
+          <t>1,18; 5,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,35</t>
+          <t>0,6; 4,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,58; 16,84</t>
+          <t>10,65; 16,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,46</t>
+          <t>0,39; 3,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,81</t>
+          <t>1,42; 5,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,71; 14,99</t>
+          <t>9,76; 15,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,63</t>
+          <t>1,33; 4,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,02</t>
+          <t>1,27; 4,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,98; 15,13</t>
+          <t>10,88; 15,03</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,25</t>
+          <t>1,38; 4,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,37</t>
+          <t>1,17; 3,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,38</t>
+          <t>3,91; 7,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,71</t>
+          <t>0,76; 2,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,22</t>
+          <t>2,8; 6,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,42</t>
+          <t>5,3; 8,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,02</t>
+          <t>1,27; 2,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,49</t>
+          <t>2,3; 4,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,67</t>
+          <t>5,06; 7,41</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,48</t>
+          <t>0,14; 1,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,1</t>
+          <t>0,6; 2,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,55</t>
+          <t>1,19; 3,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,82</t>
+          <t>0,4; 1,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,46</t>
+          <t>0,25; 1,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,39</t>
+          <t>1,65; 3,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,3</t>
+          <t>0,35; 1,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,52</t>
+          <t>0,5; 1,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,6</t>
+          <t>1,58; 2,78</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,04</t>
+          <t>1,11; 2,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,94</t>
+          <t>1,07; 1,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,18</t>
+          <t>4,05; 5,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,35</t>
+          <t>1,41; 2,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,59</t>
+          <t>1,56; 2,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,96</t>
+          <t>4,14; 5,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,06</t>
+          <t>1,41; 2,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,09</t>
+          <t>1,45; 2,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,82; 4,94</t>
+          <t>4,23; 5,05</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>12353</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1847; 11486</t>
+          <t>1852; 10969</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2842; 14756</t>
+          <t>3142; 14208</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2125; 10904</t>
+          <t>2905; 11769</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2763; 14955</t>
+          <t>2969; 14346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3813; 15795</t>
+          <t>3793; 15577</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3252; 10422</t>
+          <t>3416; 10934</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6167; 19984</t>
+          <t>6425; 21132</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9166; 25626</t>
+          <t>8764; 24289</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6969; 17966</t>
+          <t>7767; 18999</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>22192</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 12842</t>
+          <t>0; 11893</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>738; 7591</t>
+          <t>741; 7899</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5919; 20303</t>
+          <t>6219; 21118</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7690; 24348</t>
+          <t>7850; 25010</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2237; 12878</t>
+          <t>2182; 12580</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5837; 16104</t>
+          <t>5528; 16667</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8686; 28440</t>
+          <t>9557; 28459</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3808; 16081</t>
+          <t>3803; 15949</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13658; 30938</t>
+          <t>15093; 33547</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49859</t>
+          <t>49271</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1382; 13338</t>
+          <t>1387; 13915</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5936</t>
+          <t>0; 5649</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21761; 38911</t>
+          <t>20592; 38846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1975; 11419</t>
+          <t>2002; 11362</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>902; 9215</t>
+          <t>886; 8257</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14714; 27689</t>
+          <t>14289; 27423</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5132; 20644</t>
+          <t>4983; 18861</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1700; 11313</t>
+          <t>1839; 12340</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40002; 62217</t>
+          <t>39688; 61221</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25459</t>
+          <t>27650</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>965; 8222</t>
+          <t>967; 8121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2798; 15345</t>
+          <t>3036; 14806</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5571; 16625</t>
+          <t>5885; 18381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1956; 11968</t>
+          <t>1895; 11097</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 11052</t>
+          <t>0; 10937</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8729; 22637</t>
+          <t>12001; 23087</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4057; 16226</t>
+          <t>3854; 15607</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4848; 20467</t>
+          <t>4715; 20092</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17045; 34614</t>
+          <t>20848; 37341</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29916</t>
+          <t>32182</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3054; 15092</t>
+          <t>3244; 15062</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 10822</t>
+          <t>0; 9434</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9050; 19749</t>
+          <t>9591; 20938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6233; 21306</t>
+          <t>6264; 20991</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4245; 15982</t>
+          <t>4303; 16508</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12278; 21809</t>
+          <t>12745; 23080</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11667; 29518</t>
+          <t>12120; 31144</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5483; 19733</t>
+          <t>5987; 21125</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23537; 37579</t>
+          <t>25318; 40098</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36257</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>32086</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>67695</t>
+          <t>68731</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3833; 15517</t>
+          <t>3233; 15324</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2018; 11453</t>
+          <t>1572; 11468</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28514; 45410</t>
+          <t>28839; 45565</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1003; 9610</t>
+          <t>1093; 9667</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4068; 15857</t>
+          <t>3868; 16019</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24897; 38439</t>
+          <t>25690; 41095</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6266; 20051</t>
+          <t>7350; 22327</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7099; 21578</t>
+          <t>6828; 21435</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57756; 79565</t>
+          <t>58066; 80250</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>39683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43775</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>77387</t>
+          <t>91098</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9104; 28160</t>
+          <t>9159; 27283</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7657; 22114</t>
+          <t>7690; 22209</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23924; 45946</t>
+          <t>28032; 53916</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5336; 18780</t>
+          <t>5267; 18905</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21075; 42975</t>
+          <t>19373; 42832</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20433; 62951</t>
+          <t>40855; 64980</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17389; 40968</t>
+          <t>17202; 39627</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>32127; 60484</t>
+          <t>31002; 57523</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>49306; 98121</t>
+          <t>75295; 110321</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>35143</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1112; 11530</t>
+          <t>1105; 10684</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4523; 16369</t>
+          <t>4698; 16906</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5660; 23645</t>
+          <t>9488; 23941</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3347; 14989</t>
+          <t>3303; 14726</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2070; 12047</t>
+          <t>2095; 12719</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11588; 24247</t>
+          <t>13722; 27769</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6479; 20802</t>
+          <t>5567; 21270</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8215; 24451</t>
+          <t>7974; 23799</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18709; 42696</t>
+          <t>25694; 45263</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>164110</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>160400</t>
+          <t>174510</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>314536</t>
+          <t>338620</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>38818; 69833</t>
+          <t>38013; 68462</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>36588; 65709</t>
+          <t>36336; 64386</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118802; 179133</t>
+          <t>143078; 185982</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50402; 83422</t>
+          <t>50236; 83816</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>57185; 91946</t>
+          <t>55309; 91540</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>130509; 181385</t>
+          <t>154437; 193746</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98274; 144032</t>
+          <t>98281; 147293</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>99982; 145331</t>
+          <t>100489; 148343</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>272030; 351359</t>
+          <t>307362; 366562</t>
         </is>
       </c>
     </row>
